--- a/data/trans_dic/IP11C$ingresado-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,21</t>
+          <t>0,0; 67,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,78</t>
+          <t>0,0; 27,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,38</t>
+          <t>0,0; 24,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 17,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,16</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 28,5</t>
+          <t>2,8; 27,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,72</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,12</t>
+          <t>1,61; 15,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 18,61</t>
+          <t>3,0; 18,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,8</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,94</t>
+          <t>0,0; 24,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,73</t>
+          <t>1,3; 11,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,78</t>
+          <t>2,33; 11,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 16,44</t>
+          <t>2,39; 18,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 14,99</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,31</t>
+          <t>0,0; 38,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,6</t>
+          <t>0,0; 65,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,54</t>
+          <t>0,0; 31,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,83</t>
+          <t>0,0; 34,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,11</t>
+          <t>0,0; 35,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,96</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 25,63</t>
+          <t>2,54; 27,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,7</t>
+          <t>3,16; 37,0</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,51</t>
+          <t>2,15; 12,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 20,42</t>
+          <t>2,0; 20,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 26,27</t>
+          <t>2,48; 29,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,22</t>
+          <t>1,78; 12,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,19</t>
+          <t>3,57; 14,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 14,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,48</t>
+          <t>1,33; 8,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,87</t>
+          <t>3,88; 11,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,43</t>
+          <t>1,89; 12,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,48</t>
+          <t>2,72; 15,29</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2717</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3511</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4120</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3669</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3579</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>463; 4616</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2551</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>595; 5649</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1345; 8387</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5875</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3604</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>755; 6418</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1929; 9750</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1143; 9062</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3862</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1151</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2585</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3773</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2149</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5549</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2782</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2342</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>651; 7154</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>411; 4806</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8782</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4102</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6493</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>466; 4782</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>426; 5006</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>828; 5819</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2622; 10939</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6094</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1090; 6957</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4854; 14751</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7742</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1118; 6299</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$ingresado-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Estudios-trans_dic.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,04</t>
+          <t>0,0; 65,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,9</t>
+          <t>0,0; 27,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,76</t>
+          <t>0,0; 26,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,43</t>
+          <t>0,0; 17,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,43</t>
+          <t>0,0; 9,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 27,97</t>
+          <t>2,81; 25,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,15</t>
+          <t>0,0; 28,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 15,3</t>
+          <t>1,6; 15,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 18,68</t>
+          <t>3,01; 17,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,72</t>
+          <t>0,0; 18,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,44</t>
+          <t>0,0; 20,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,07</t>
+          <t>1,27; 11,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,77</t>
+          <t>2,52; 11,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 18,92</t>
+          <t>2,55; 16,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,99</t>
+          <t>0,0; 14,75</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,86</t>
+          <t>0,0; 40,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,96</t>
+          <t>0,0; 66,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,77</t>
+          <t>0,0; 41,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,9</t>
+          <t>0,0; 34,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,06</t>
+          <t>0,0; 35,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,85</t>
+          <t>0,0; 15,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 27,94</t>
+          <t>2,55; 26,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 37,0</t>
+          <t>3,08; 36,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 11,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,56</t>
+          <t>2,13; 12,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 20,46</t>
+          <t>2,03; 19,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 29,19</t>
+          <t>2,32; 26,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,51</t>
+          <t>1,4; 12,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,91</t>
+          <t>3,58; 15,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 14,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,93</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,5</t>
+          <t>1,47; 8,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,79</t>
+          <t>3,98; 11,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,08</t>
+          <t>1,79; 12,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,29</t>
+          <t>2,8; 16,65</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2717</t>
+          <t>0; 2666</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 3450</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4120</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3669</t>
+          <t>0; 3754</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>0; 3465</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>463; 4616</t>
+          <t>463; 4235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2551</t>
+          <t>0; 3123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>595; 5649</t>
+          <t>591; 5721</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1345; 8387</t>
+          <t>1350; 8006</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5875</t>
+          <t>0; 5656</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3604</t>
+          <t>0; 3005</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755; 6418</t>
+          <t>737; 6920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1929; 9750</t>
+          <t>2087; 9364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1143; 9062</t>
+          <t>1220; 7756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 3799</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3773</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2149</t>
+          <t>0; 2804</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5549</t>
+          <t>0; 5457</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2782</t>
+          <t>0; 2853</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2342</t>
+          <t>0; 2666</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651; 7154</t>
+          <t>652; 6674</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>411; 4806</t>
+          <t>400; 4764</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 3891</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1113; 6493</t>
+          <t>1104; 6523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>466; 4782</t>
+          <t>475; 4666</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>426; 5006</t>
+          <t>398; 4493</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>828; 5819</t>
+          <t>649; 6043</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2622; 10939</t>
+          <t>2626; 11425</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3831</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090; 6957</t>
+          <t>1203; 7132</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4854; 14751</t>
+          <t>4976; 14887</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1208; 7742</t>
+          <t>1150; 8103</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1118; 6299</t>
+          <t>1151; 6858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$ingresado-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,27 +654,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>16,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,77</t>
+          <t>0,0; 29,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,41</t>
+          <t>0,0; 67,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,66</t>
+          <t>0,0; 25,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,84</t>
+          <t>1,61; 14,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,13</t>
+          <t>3,15; 18,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 25,66</t>
+          <t>0,0; 16,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 26,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 15,49</t>
+          <t>0,0; 17,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 17,83</t>
+          <t>0,0; 9,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,02</t>
+          <t>2,78; 28,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,38</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,94</t>
+          <t>1,27; 11,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 11,3</t>
+          <t>2,64; 11,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 16,19</t>
+          <t>2,31; 16,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,75</t>
+          <t>0,0; 16,46</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,69%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,73</t>
+          <t>0,0; 31,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,36</t>
+          <t>0,0; 39,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,32</t>
+          <t>0,0; 45,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,94</t>
+          <t>0,0; 63,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,77</t>
+          <t>0,0; 16,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 26,06</t>
+          <t>2,49; 25,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 36,68</t>
+          <t>1,55; 33,33</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>1,29; 13,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,61</t>
+          <t>2,85; 15,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,97</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 26,2</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,99</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,57</t>
+          <t>1,29; 11,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>2,01; 20,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>2,09; 25,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,72</t>
+          <t>1,47; 8,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,9</t>
+          <t>3,77; 11,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 12,64</t>
+          <t>1,76; 12,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,65</t>
+          <t>2,2; 15,23</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1441,27 +1441,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>675</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2666</t>
+          <t>0; 3747</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 2724</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 4223</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1576,37 +1576,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1089</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>592</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1218</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3754</t>
+          <t>595; 5215</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3465</t>
+          <t>1413; 8355</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>463; 4235</t>
+          <t>0; 5273</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 3605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>591; 5721</t>
+          <t>0; 3604</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1350; 8006</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5656</t>
+          <t>458; 4703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3005</t>
+          <t>0; 3181</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>737; 6920</t>
+          <t>738; 6799</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2087; 9364</t>
+          <t>2187; 9763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1220; 7756</t>
+          <t>1104; 7872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3799</t>
+          <t>0; 4068</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,49 +1852,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>1329</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>2585</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1487</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2201</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3955</t>
+          <t>0; 5061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 2902</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2804</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5457</t>
+          <t>0; 4398</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2853</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2666</t>
+          <t>0; 2867</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>652; 6674</t>
+          <t>638; 6563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>400; 4764</t>
+          <t>193; 4149</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3093</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2705</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>599; 6149</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1104; 6523</t>
+          <t>2089; 11146</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>475; 4666</t>
+          <t>0; 5466</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>398; 4493</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>649; 6043</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2626; 11425</t>
+          <t>669; 5952</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>471; 4772</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>359; 4385</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1203; 7132</t>
+          <t>1204; 6940</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4976; 14887</t>
+          <t>4717; 14850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1150; 8103</t>
+          <t>1126; 7966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1151; 6858</t>
+          <t>869; 6005</t>
         </is>
       </c>
     </row>
